--- a/experiments/results/resnet18/CIFAR-10/DICE/adaptive/max/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/DICE/adaptive/max/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -617,6 +617,55 @@
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>dice_p=70,ash_p=None,react_th=None,scale_th=3.0,type=max</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>42.31</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>92.01000000000001</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.18</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>17.02</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>97.17</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>97.26000000000001</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=70,ash_p=None,react_th=None,scale_th=10.0,type=max</t>
         </is>
       </c>
     </row>
